--- a/service/infa/Удобный слой над API python.xlsx
+++ b/service/infa/Удобный слой над API python.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18432" windowHeight="7590" firstSheet="2" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18432" windowHeight="7590" firstSheet="5" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Структура папок2" sheetId="7" r:id="rId6"/>
     <sheet name="Методы General" sheetId="6" r:id="rId7"/>
     <sheet name="Структура Part" sheetId="8" r:id="rId8"/>
+    <sheet name="Контекст" sheetId="9" r:id="rId9"/>
+    <sheet name="Шаблон детали" sheetId="10" r:id="rId10"/>
+    <sheet name="Лист4" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -131,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="606">
   <si>
     <t>inventor_api.py    = действия и логика</t>
   </si>
@@ -1797,6 +1800,588 @@
   </si>
   <si>
     <t>Возвращает рабочую точку по номеру или имени.</t>
+  </si>
+  <si>
+    <t>Нужно дополнить библиотеку inventor_service, чтобы рабочий проект “Присадка кодом Python” мог не обращаться к низкоуровневому Inventor API напрямую. Сейчас большая часть уже использует Inventor, но остаются прямые вызовы к эскизам, линиям, проекциям и рабочим плоскостям.</t>
+  </si>
+  <si>
+    <t>Нужные методы в библиотеке:</t>
+  </si>
+  <si>
+    <t>def add_sketch_line(self, sketch, start_point, end_point, construction=False):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Создать линию в эскизе через SketchLines.AddByTwoPoints."""</t>
+  </si>
+  <si>
+    <t>Используется вместо:</t>
+  </si>
+  <si>
+    <t>sketch.SketchLines.AddByTwoPoints(p1, p2)</t>
+  </si>
+  <si>
+    <t>Нужно в:</t>
+  </si>
+  <si>
+    <t>sketch/drilling_sketch.py</t>
+  </si>
+  <si>
+    <t>stiajka/stiajka.py</t>
+  </si>
+  <si>
+    <t>def project_entity_to_sketch(self, sketch, entity, construction=None, ignore_errors=False):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Спроецировать edge/point/entity в эскиз через sketch.AddByProjectingEntity."""</t>
+  </si>
+  <si>
+    <t>sketch.AddByProjectingEntity(edge)</t>
+  </si>
+  <si>
+    <t>sketch.AddByProjectingEntity(source_point)</t>
+  </si>
+  <si>
+    <t>Желательно возвращать созданный объект. Если construction не None, пробовать выставить projected.Construction = construction.</t>
+  </si>
+  <si>
+    <t>def sketch_points(self, sketch, hole_center=None):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Вернуть список SketchPoint из sketch.SketchPoints."""</t>
+  </si>
+  <si>
+    <t>Используется вместо циклов:</t>
+  </si>
+  <si>
+    <t>for i in range(1, sketch.SketchPoints.Count + 1):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    point = sketch.SketchPoints.Item(i)</t>
+  </si>
+  <si>
+    <t>Если hole_center=True, вернуть только точки с point.HoleCenter == True.</t>
+  </si>
+  <si>
+    <t>def sketch_point_count(self, sketch):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Вернуть sketch.SketchPoints.Count."""</t>
+  </si>
+  <si>
+    <t>Полезно для проверок пустого эскиза и логов.</t>
+  </si>
+  <si>
+    <t>def sketch_dimension_constraints(self, sketch):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Вернуть список DimensionConstraints."""</t>
+  </si>
+  <si>
+    <t>for i in range(1, sketch.DimensionConstraints.Count + 1):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    dim = sketch.DimensionConstraints.Item(i)</t>
+  </si>
+  <si>
+    <t>def sketch_dimension_count(self, sketch):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Вернуть sketch.DimensionConstraints.Count."""</t>
+  </si>
+  <si>
+    <t>def add_two_point_dimension(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    self,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    sketch,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    point1,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    point2,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    orientation,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    text_point,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    driven=False,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    expression=None,</t>
+  </si>
+  <si>
+    <t>):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Универсальный wrapper для DimensionConstraints.AddTwoPointDistance."""</t>
+  </si>
+  <si>
+    <t>Сейчас есть add_aligned_dimension, но нужны еще horizontal/vertical. Метод должен принимать строковые ориентации "aligned", "horizontal", "vertical" через уже существующий dimension_orientation().</t>
+  </si>
+  <si>
+    <t>def set_sketch_defer_updates(self, sketch, value):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Безопасно выставить sketch.DeferUpdates и вернуть предыдущее значение или None."""</t>
+  </si>
+  <si>
+    <t>И желательно context manager:</t>
+  </si>
+  <si>
+    <t>@contextmanager</t>
+  </si>
+  <si>
+    <t>def deferred_sketch_updates(self, sketch):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Временно включить DeferUpdates=True и восстановить исходное значение."""</t>
+  </si>
+  <si>
+    <t>def set_sketch_dimensions_visible(self, sketch, visible):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Безопасно выставить sketch.DimensionsVisible."""</t>
+  </si>
+  <si>
+    <t>Заменит локальный hide_sketch_dimensions.</t>
+  </si>
+  <si>
+    <t>def set_entity_construction(self, entity, construction=True):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Безопасно выставить entity.Construction."""</t>
+  </si>
+  <si>
+    <t>Используется для линий и проекций.</t>
+  </si>
+  <si>
+    <t>def set_point_hole_center(self, point, hole_center=True):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Безопасно выставить point.HoleCenter."""</t>
+  </si>
+  <si>
+    <t>Сейчас частично есть mark_as_hole_centers(points), но нужен метод для одной точки.</t>
+  </si>
+  <si>
+    <t>def add_ground_constraint(self, sketch, entity, ignore_errors=True):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Добавить GeometricConstraints.AddGround(entity)."""</t>
+  </si>
+  <si>
+    <t>def add_midpoint_constraint(self, sketch, point_or_line_point, line, ignore_errors=True):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Wrapper для GeometricConstraints.AddMidpoint."""</t>
+  </si>
+  <si>
+    <t>def add_coincident_constraint(self, sketch, entity1, entity2, ignore_errors=True):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Wrapper для GeometricConstraints.AddCoincident."""</t>
+  </si>
+  <si>
+    <t>def add_perpendicular_constraint(self, sketch, line1, line2, ignore_errors=True):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Wrapper для GeometricConstraints.AddPerpendicular."""</t>
+  </si>
+  <si>
+    <t>def add_parallel_constraint(self, sketch, line1, line2, ignore_errors=True):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Wrapper для GeometricConstraints.AddParallel."""</t>
+  </si>
+  <si>
+    <t>def add_symmetry_constraint(self, sketch, entity1, entity2, symmetry_line, ignore_errors=True):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Wrapper для GeometricConstraints.AddSymmetry."""</t>
+  </si>
+  <si>
+    <t>def all_sketches(self, component_definition=None):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Вернуть список всех эскизов детали."""</t>
+  </si>
+  <si>
+    <t>for i in range(1, component_definition.Sketches.Count + 1):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    sketch = component_definition.Sketches.Item(i)</t>
+  </si>
+  <si>
+    <t>def sketches_by_prefix(self, prefix, component_definition=None):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Вернуть эскизы, имя которых начинается с prefix."""</t>
+  </si>
+  <si>
+    <t>def unique_sketch_name(self, base, sketches=None):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Вернуть свободное имя эскиза."""</t>
+  </si>
+  <si>
+    <t>Сейчас эта логика дублируется в нескольких файлах.</t>
+  </si>
+  <si>
+    <t>def sketch_has_lines_or_points(self, sketch):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Вернуть True, если в эскизе есть линии или точки."""</t>
+  </si>
+  <si>
+    <t>Заменит прямой доступ:</t>
+  </si>
+  <si>
+    <t>sketch.SketchLines.Count == 0 and sketch.SketchPoints.Count == 0</t>
+  </si>
+  <si>
+    <t>def create_point3d(self, x, y, z):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Создать 3D-точку через transient_geometry.CreatePoint."""</t>
+  </si>
+  <si>
+    <t>Сейчас в stiajka.py есть прямые вызовы:</t>
+  </si>
+  <si>
+    <t>tg.CreatePoint(...)</t>
+  </si>
+  <si>
+    <t>def project_point_to_plane(self, point, planar_entity):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Спроецировать 3D-точку на плоскость planar_entity/face/workplane и вернуть Point3d."""</t>
+  </si>
+  <si>
+    <t>В stiajka.py сейчас есть локальная функция project_point_to_face_plane(tg, point, face).</t>
+  </si>
+  <si>
+    <t>def create_work_plane_by_line_plane_angle(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    line,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    plane,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    angle,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    construction=True,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    component_definition=None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Wrapper для WorkPlanes.AddByLinePlaneAndAngle."""</t>
+  </si>
+  <si>
+    <t>Нужен для замены прямого вызова:</t>
+  </si>
+  <si>
+    <t>component_definition.WorkPlanes.AddByLinePlaneAndAngle(...)</t>
+  </si>
+  <si>
+    <t>def model_to_sketch_points_from_vertices(self, sketch, vertices):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Преобразовать vertices.Item(...).Point в 2D-точки эскиза."""</t>
+  </si>
+  <si>
+    <t>Можно обойтись существующими face_vertex_points_in_sketch, но для общих коллекций вершин удобно.</t>
+  </si>
+  <si>
+    <t>def sketch_to_model_points(self, sketch, sketch_points):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """Преобразовать SketchPoint.Geometry в 3D-точки модели через SketchToModelSpace."""</t>
+  </si>
+  <si>
+    <t>Приоритет внедрения:</t>
+  </si>
+  <si>
+    <t>1. add_sketch_line</t>
+  </si>
+  <si>
+    <t>2. project_entity_to_sketch</t>
+  </si>
+  <si>
+    <t>3. sketch_points, sketch_point_count</t>
+  </si>
+  <si>
+    <t>4. sketch_dimension_constraints, sketch_dimension_count</t>
+  </si>
+  <si>
+    <t>5. add_two_point_dimension</t>
+  </si>
+  <si>
+    <t>6. constraint wrappers: coincident, midpoint, perpendicular, parallel, symmetry, ground</t>
+  </si>
+  <si>
+    <t>7. create_point3d, project_point_to_plane</t>
+  </si>
+  <si>
+    <t>8. all_sketches, sketches_by_prefix, unique_sketch_name</t>
+  </si>
+  <si>
+    <t>9. deferred_sketch_updates, set_sketch_dimensions_visible</t>
+  </si>
+  <si>
+    <t>10. create_work_plane_by_line_plane_angle</t>
+  </si>
+  <si>
+    <t>После добавления этих методов в библиотеку можно будет заменить оставшиеся прямые вызовы в проекте:</t>
+  </si>
+  <si>
+    <t>SketchLines.AddByTwoPoints</t>
+  </si>
+  <si>
+    <t>SketchLines.Count</t>
+  </si>
+  <si>
+    <t>SketchLines.Item</t>
+  </si>
+  <si>
+    <t>SketchPoints.Add</t>
+  </si>
+  <si>
+    <t>SketchPoints.Count</t>
+  </si>
+  <si>
+    <t>SketchPoints.Item</t>
+  </si>
+  <si>
+    <t>DimensionConstraints.Item</t>
+  </si>
+  <si>
+    <t>AddByProjectingEntity</t>
+  </si>
+  <si>
+    <t>TransientGeometry.CreatePoint</t>
+  </si>
+  <si>
+    <t>WorkPlanes.AddByLinePlaneAndAngle</t>
+  </si>
+  <si>
+    <t>component_definition.Sketches.Item(...)</t>
+  </si>
+  <si>
+    <t>Нужно дополнить библиотеку inventor_service, чтобы рабочий проект “Присадка кодом Python” мог не обращаться к низкоуровневому Inventor API напрямую. Сейчас большая часть уже использует Inventor, но остаются прямые вызовы к эскизам, линиям, проекциям и рабочим плоскостям.
+Нужные методы в библиотеке:
+def add_sketch_line(self, sketch, start_point, end_point, construction=False):
+    """Создать линию в эскизе через SketchLines.AddByTwoPoints."""
+Используется вместо:
+sketch.SketchLines.AddByTwoPoints(p1, p2)
+Нужно в:
+- sketch/drilling_sketch.py
+- stiajka/stiajka.py
+def project_entity_to_sketch(self, sketch, entity, construction=None, ignore_errors=False):
+    """Спроецировать edge/point/entity в эскиз через sketch.AddByProjectingEntity."""
+Используется вместо:
+sketch.AddByProjectingEntity(edge)
+sketch.AddByProjectingEntity(source_point)
+Желательно возвращать созданный объект. Если construction не None, пробовать выставить projected.Construction = construction.
+def sketch_points(self, sketch, hole_center=None):
+    """Вернуть список SketchPoint из sketch.SketchPoints."""
+Используется вместо циклов:
+for i in range(1, sketch.SketchPoints.Count + 1):
+    point = sketch.SketchPoints.Item(i)
+Если hole_center=True, вернуть только точки с point.HoleCenter == True.
+def sketch_point_count(self, sketch):
+    """Вернуть sketch.SketchPoints.Count."""
+Полезно для проверок пустого эскиза и логов.
+def sketch_dimension_constraints(self, sketch):
+    """Вернуть список DimensionConstraints."""
+Используется вместо:
+for i in range(1, sketch.DimensionConstraints.Count + 1):
+    dim = sketch.DimensionConstraints.Item(i)
+def sketch_dimension_count(self, sketch):
+    """Вернуть sketch.DimensionConstraints.Count."""
+def add_two_point_dimension(
+    self,
+    sketch,
+    point1,
+    point2,
+    orientation,
+    text_point,
+    driven=False,
+    expression=None,
+):
+    """Универсальный wrapper для DimensionConstraints.AddTwoPointDistance."""
+Сейчас есть add_aligned_dimension, но нужны еще horizontal/vertical. Метод должен принимать строковые ориентации "aligned", "horizontal", "vertical" через уже существующий dimension_orientation().
+def set_sketch_defer_updates(self, sketch, value):
+    """Безопасно выставить sketch.DeferUpdates и вернуть предыдущее значение или None."""
+И желательно context manager:
+@contextmanager
+def deferred_sketch_updates(self, sketch):
+    """Временно включить DeferUpdates=True и восстановить исходное значение."""
+def set_sketch_dimensions_visible(self, sketch, visible):
+    """Безопасно выставить sketch.DimensionsVisible."""
+Заменит локальный hide_sketch_dimensions.
+def set_entity_construction(self, entity, construction=True):
+    """Безопасно выставить entity.Construction."""
+Используется для линий и проекций.
+def set_point_hole_center(self, point, hole_center=True):
+    """Безопасно выставить point.HoleCenter."""
+Сейчас частично есть mark_as_hole_centers(points), но нужен метод для одной точки.
+def add_ground_constraint(self, sketch, entity, ignore_errors=True):
+    """Добавить GeometricConstraints.AddGround(entity)."""
+def add_midpoint_constraint(self, sketch, point_or_line_point, line, ignore_errors=True):
+    """Wrapper для GeometricConstraints.AddMidpoint."""
+def add_coincident_constraint(self, sketch, entity1, entity2, ignore_errors=True):
+    """Wrapper для GeometricConstraints.AddCoincident."""
+def add_perpendicular_constraint(self, sketch, line1, line2, ignore_errors=True):
+    """Wrapper для GeometricConstraints.AddPerpendicular."""
+def add_parallel_constraint(self, sketch, line1, line2, ignore_errors=True):
+    """Wrapper для GeometricConstraints.AddParallel."""
+def add_symmetry_constraint(self, sketch, entity1, entity2, symmetry_line, ignore_errors=True):
+    """Wrapper для GeometricConstraints.AddSymmetry."""
+def all_sketches(self, component_definition=None):
+    """Вернуть список всех эскизов детали."""
+Используется вместо:
+for i in range(1, component_definition.Sketches.Count + 1):
+    sketch = component_definition.Sketches.Item(i)
+def sketches_by_prefix(self, prefix, component_definition=None):
+    """Вернуть эскизы, имя которых начинается с prefix."""
+def unique_sketch_name(self, base, sketches=None):
+    """Вернуть свободное имя эскиза."""
+Сейчас эта логика дублируется в нескольких файлах.
+def sketch_has_lines_or_points(self, sketch):
+    """Вернуть True, если в эскизе есть линии или точки."""
+Заменит прямой доступ:
+sketch.SketchLines.Count == 0 and sketch.SketchPoints.Count == 0
+def create_point3d(self, x, y, z):
+    """Создать 3D-точку через transient_geometry.CreatePoint."""
+Сейчас в stiajka.py есть прямые вызовы:
+tg.CreatePoint(...)
+def project_point_to_plane(self, point, planar_entity):
+    """Спроецировать 3D-точку на плоскость planar_entity/face/workplane и вернуть Point3d."""
+В stiajka.py сейчас есть локальная функция project_point_to_face_plane(tg, point, face).
+def create_work_plane_by_line_plane_angle(
+    self,
+    line,
+    plane,
+    angle,
+    construction=True,
+    component_definition=None,
+):
+    """Wrapper для WorkPlanes.AddByLinePlaneAndAngle."""
+Нужен для замены прямого вызова:
+component_definition.WorkPlanes.AddByLinePlaneAndAngle(...)
+def model_to_sketch_points_from_vertices(self, sketch, vertices):
+    """Преобразовать vertices.Item(...).Point в 2D-точки эскиза."""
+Можно обойтись существующими face_vertex_points_in_sketch, но для общих коллекций вершин удобно.
+def sketch_to_model_points(self, sketch, sketch_points):
+    """Преобразовать SketchPoint.Geometry в 3D-точки модели через SketchToModelSpace."""
+Приоритет внедрения:
+1. add_sketch_line
+2. project_entity_to_sketch
+3. sketch_points, sketch_point_count
+4. sketch_dimension_constraints, sketch_dimension_count
+5. add_two_point_dimension
+6. constraint wrappers: coincident, midpoint, perpendicular, parallel, symmetry, ground
+7. create_point3d, project_point_to_plane
+8. all_sketches, sketches_by_prefix, unique_sketch_name
+9. deferred_sketch_updates, set_sketch_dimensions_visible
+10. create_work_plane_by_line_plane_angle
+После добавления этих методов в библиотеку можно будет заменить оставшиеся прямые вызовы в проекте:
+- SketchLines.AddByTwoPoints
+- SketchLines.Count
+- SketchLines.Item
+- SketchPoints.Add
+- SketchPoints.Count
+- SketchPoints.Item
+- DimensionConstraints.Item
+- AddByProjectingEntity
+- TransientGeometry.CreatePoint
+- WorkPlanes.AddByLinePlaneAndAngle
+- component_definition.Sketches.Item(...)</t>
+  </si>
+  <si>
+    <t>Правильная цель следующего прохода: оставить прямой Inventor API только внутри 01_inventor_service, а в проекте Присадка кодом Python убрать такие обращения совсем.     Сделай</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шаблон детали должен содержать </t>
+  </si>
+  <si>
+    <t>Ссылку на excel  таблицу- присадку</t>
+  </si>
+  <si>
+    <t>Toлщина_каркаса</t>
+  </si>
+  <si>
+    <t>Параметры:</t>
+  </si>
+  <si>
+    <t>Желаемый_отступ_присадки_от_кромки1</t>
+  </si>
+  <si>
+    <t>Желаемый_отступ_присадки_от_ящик</t>
+  </si>
+  <si>
+    <t>1)</t>
+  </si>
+  <si>
+    <t>2)</t>
+  </si>
+  <si>
+    <t>3)</t>
+  </si>
+  <si>
+    <t>Эскизные блоки</t>
+  </si>
+  <si>
+    <t>Ответка петли</t>
+  </si>
+  <si>
+    <t>Присадка направляющих</t>
+  </si>
+  <si>
+    <t>Отверстия под опоры</t>
+  </si>
+  <si>
+    <t>Колличество_конфирматов_на каркасе</t>
+  </si>
+  <si>
+    <t>Excel</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Константы крепежа</t>
+  </si>
+  <si>
+    <t>Использует Part  и Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Управление из </t>
+  </si>
+  <si>
+    <t>Не должно быть магических цифр, только параметры Excel  и Part</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> В диалоговом окне выбираем параметр Part, так мы привязываемся к пареметрам детали</t>
+  </si>
+  <si>
+    <t>Нужно четко разделить константы и индивидуальные параметры детали</t>
+  </si>
+  <si>
+    <t>Динамические параметры</t>
   </si>
 </sst>
 </file>
@@ -1990,7 +2575,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2015,8 +2600,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2074,11 +2665,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2144,9 +2797,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2172,11 +2822,29 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2807,6 +3475,161 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="17.68359375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="14.7" thickBot="1"/>
+    <row r="2" spans="1:9">
+      <c r="A2" s="49" t="s">
+        <v>601</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>596</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="I2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="14.7" thickBot="1">
+      <c r="A3" s="50"/>
+      <c r="B3" s="44" t="s">
+        <v>597</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>605</v>
+      </c>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="14.4" customHeight="1">
+      <c r="A5" s="51" t="s">
+        <v>602</v>
+      </c>
+      <c r="B5" t="s">
+        <v>598</v>
+      </c>
+      <c r="C5" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="51"/>
+      <c r="F6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="51"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="51"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>588</v>
+      </c>
+      <c r="B11" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>589</v>
+      </c>
+      <c r="B12" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="C13" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="C14" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="C15" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="C16" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="C17" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="C18" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>590</v>
+      </c>
+      <c r="B21" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="C22" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="C23" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="C24" t="s">
+        <v>594</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:H30"/>
@@ -4070,50 +4893,50 @@
   <dimension ref="A2:J39"/>
   <sheetFormatPr defaultColWidth="20.05078125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.7890625" style="36" customWidth="1"/>
-    <col min="2" max="2" width="12.20703125" style="36" customWidth="1"/>
-    <col min="3" max="3" width="27.1015625" style="36" customWidth="1"/>
-    <col min="4" max="4" width="3" style="36" customWidth="1"/>
-    <col min="5" max="5" width="28.5234375" style="36" customWidth="1"/>
-    <col min="6" max="6" width="3" style="36" customWidth="1"/>
-    <col min="7" max="7" width="19.83984375" style="35" customWidth="1"/>
-    <col min="8" max="8" width="3" style="35" customWidth="1"/>
-    <col min="9" max="9" width="21.41796875" style="35" customWidth="1"/>
-    <col min="10" max="10" width="3" style="35" customWidth="1"/>
-    <col min="11" max="16384" width="20.05078125" style="36"/>
+    <col min="1" max="1" width="18.7890625" style="35" customWidth="1"/>
+    <col min="2" max="2" width="12.20703125" style="35" customWidth="1"/>
+    <col min="3" max="3" width="27.1015625" style="35" customWidth="1"/>
+    <col min="4" max="4" width="3" style="35" customWidth="1"/>
+    <col min="5" max="5" width="28.5234375" style="35" customWidth="1"/>
+    <col min="6" max="6" width="3" style="35" customWidth="1"/>
+    <col min="7" max="7" width="19.83984375" style="34" customWidth="1"/>
+    <col min="8" max="8" width="3" style="34" customWidth="1"/>
+    <col min="9" max="9" width="21.41796875" style="34" customWidth="1"/>
+    <col min="10" max="10" width="3" style="34" customWidth="1"/>
+    <col min="11" max="16384" width="20.05078125" style="35"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="18.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="46" t="s">
         <v>441</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
     </row>
     <row r="3" spans="1:9" ht="20.05" customHeight="1">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="36" t="s">
         <v>364</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="37"/>
+      <c r="C3" s="36"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="37"/>
+      <c r="E3" s="36"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="37"/>
+      <c r="G3" s="36"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="37"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="20.05" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="30" t="s">
         <v>442</v>
       </c>
       <c r="C4" s="1"/>
@@ -4128,7 +4951,7 @@
       <c r="A5" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="30" t="s">
         <v>443</v>
       </c>
       <c r="C5" s="1"/>
@@ -4143,7 +4966,7 @@
       <c r="A6" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="30" t="s">
         <v>444</v>
       </c>
       <c r="C6" s="1"/>
@@ -4158,14 +4981,14 @@
       <c r="A7" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="30" t="s">
         <v>445</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="38"/>
+      <c r="G7" s="37"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
@@ -4173,7 +4996,7 @@
       <c r="A8" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="30" t="s">
         <v>446</v>
       </c>
       <c r="C8" s="1"/>
@@ -4188,7 +5011,7 @@
       <c r="A9" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>447</v>
       </c>
       <c r="C9" s="1"/>
@@ -4217,7 +5040,7 @@
       <c r="A11" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>449</v>
       </c>
       <c r="C11" s="1"/>
@@ -4279,7 +5102,7 @@
       <c r="B15" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="C15" s="39"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -4294,7 +5117,7 @@
       <c r="B16" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C16" s="39"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -4303,64 +5126,64 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:3" ht="14.4" customHeight="1">
-      <c r="C17" s="39"/>
+      <c r="C17" s="38"/>
     </row>
     <row r="18" spans="1:3" ht="14.4" customHeight="1">
-      <c r="C18" s="39"/>
+      <c r="C18" s="38"/>
     </row>
     <row r="19" spans="1:3" ht="14.4" customHeight="1">
-      <c r="C19" s="40"/>
+      <c r="C19" s="39"/>
     </row>
     <row r="21" spans="1:3" ht="14.4" customHeight="1"/>
     <row r="24" spans="1:3">
-      <c r="C24" s="40"/>
+      <c r="C24" s="39"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="39" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="40" t="s">
+      <c r="A30" s="39" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="40" t="s">
+      <c r="A31" s="39" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="40"/>
+      <c r="A32" s="39"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="40"/>
+      <c r="A33" s="39"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="40"/>
+      <c r="A34" s="39"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="40" t="s">
+      <c r="A35" s="39" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="40" t="s">
+      <c r="A36" s="39" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="40" t="s">
+      <c r="A37" s="39" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="40" t="s">
+      <c r="A38" s="39" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="40" t="s">
+      <c r="A39" s="39" t="s">
         <v>363</v>
       </c>
     </row>
@@ -4388,23 +5211,23 @@
       <c r="B2" s="27" t="s">
         <v>416</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="48" t="s">
         <v>408</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:14">
       <c r="B3" t="s">
         <v>373</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
     </row>
     <row r="4" spans="1:14">
       <c r="B4" t="s">
@@ -4434,73 +5257,73 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="29" t="s">
         <v>435</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="33" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="B9" s="30"/>
+      <c r="B9" s="29"/>
       <c r="D9" t="s">
         <v>226</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="33" t="s">
         <v>412</v>
       </c>
       <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="B10" s="30"/>
+      <c r="B10" s="29"/>
       <c r="D10" t="s">
         <v>328</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="33" t="s">
         <v>409</v>
       </c>
       <c r="H10" s="27"/>
     </row>
     <row r="11" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="B11" s="30"/>
+      <c r="B11" s="29"/>
       <c r="D11" t="s">
         <v>205</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="33" t="s">
         <v>410</v>
       </c>
       <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="B12" s="30"/>
+      <c r="B12" s="29"/>
       <c r="D12" t="s">
         <v>417</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="33" t="s">
         <v>411</v>
       </c>
       <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="B13" s="30"/>
+      <c r="B13" s="29"/>
       <c r="D13" t="s">
         <v>349</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="33" t="s">
         <v>413</v>
       </c>
       <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="B14" s="30"/>
-      <c r="G14" s="34"/>
+      <c r="B14" s="29"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="29" t="s">
         <v>436</v>
       </c>
-      <c r="G15" s="34" t="s">
+      <c r="G15" s="33" t="s">
         <v>422</v>
       </c>
     </row>
@@ -4516,7 +5339,7 @@
       <c r="D17" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="30" t="s">
         <v>419</v>
       </c>
       <c r="H17" s="27"/>
@@ -4525,7 +5348,7 @@
       <c r="D18" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="30" t="s">
         <v>420</v>
       </c>
       <c r="H18" s="27"/>
@@ -4534,7 +5357,7 @@
       <c r="D19" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="30" t="s">
         <v>421</v>
       </c>
       <c r="H19" s="27"/>
@@ -4570,7 +5393,7 @@
       <c r="B25" s="27" t="s">
         <v>437</v>
       </c>
-      <c r="G25" s="34" t="s">
+      <c r="G25" s="33" t="s">
         <v>439</v>
       </c>
       <c r="N25" s="27"/>
@@ -4612,7 +5435,7 @@
       <c r="B29" s="27" t="s">
         <v>423</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="32" t="s">
         <v>341</v>
       </c>
       <c r="G29" s="27" t="s">
@@ -4623,7 +5446,7 @@
       <c r="B30" s="27" t="s">
         <v>423</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="31" t="s">
         <v>344</v>
       </c>
       <c r="G30" s="27" t="s">
@@ -4634,7 +5457,7 @@
       <c r="B31" s="27" t="s">
         <v>423</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="31" t="s">
         <v>347</v>
       </c>
       <c r="G31" s="27" t="s">
@@ -4671,7 +5494,7 @@
       <c r="B36" s="27" t="s">
         <v>438</v>
       </c>
-      <c r="G36" s="34" t="s">
+      <c r="G36" s="33" t="s">
         <v>440</v>
       </c>
     </row>
@@ -4888,4 +5711,678 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:N247"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
+      <c r="B33" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
+      <c r="B36" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
+      <c r="B38" t="s">
+        <v>472</v>
+      </c>
+      <c r="N38" s="41" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14">
+      <c r="B39" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14">
+      <c r="N40" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14">
+      <c r="B41" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
+      <c r="B45" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
+      <c r="B46" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
+      <c r="B48" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2">
+      <c r="B215" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2">
+      <c r="B216" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2">
+      <c r="B220" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2">
+      <c r="B222" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2">
+      <c r="B223" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2">
+      <c r="B225" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2">
+      <c r="B226" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2">
+      <c r="B228" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2">
+      <c r="B229" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2">
+      <c r="B230" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2">
+      <c r="B231" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2">
+      <c r="B233" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2">
+      <c r="B235" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2">
+      <c r="B236" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2">
+      <c r="B237" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2">
+      <c r="B238" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2">
+      <c r="B239" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2">
+      <c r="B240" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="241" spans="2:2">
+      <c r="B241" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2">
+      <c r="B242" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2">
+      <c r="B243" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2">
+      <c r="B244" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2">
+      <c r="B245" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2">
+      <c r="B247" s="40">
+        <v>0.8979166666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>